--- a/results/accuracy_tables_sw.xlsx
+++ b/results/accuracy_tables_sw.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\UnlearningDataStreamPlayground\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1C1A6E-37AA-4FB0-903A-F00FC9107D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2655" yWindow="4395" windowWidth="28800" windowHeight="15885" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="lr_0.0001" sheetId="1" r:id="rId1"/>
@@ -23,13 +17,28 @@
     <sheet name="lr_0.0008" sheetId="8" r:id="rId8"/>
     <sheet name="lr_0.0009" sheetId="9" r:id="rId9"/>
     <sheet name="lr_0.001" sheetId="10" r:id="rId10"/>
+    <sheet name="lr_0.0011" sheetId="11" r:id="rId11"/>
+    <sheet name="lr_0.0012" sheetId="12" r:id="rId12"/>
+    <sheet name="lr_0.0013" sheetId="13" r:id="rId13"/>
+    <sheet name="lr_0.0014" sheetId="14" r:id="rId14"/>
+    <sheet name="lr_0.0015" sheetId="15" r:id="rId15"/>
+    <sheet name="lr_0.0016" sheetId="16" r:id="rId16"/>
+    <sheet name="lr_0.0017" sheetId="17" r:id="rId17"/>
+    <sheet name="lr_0.0018" sheetId="18" r:id="rId18"/>
+    <sheet name="lr_0.0019" sheetId="19" r:id="rId19"/>
+    <sheet name="lr_0.002" sheetId="20" r:id="rId20"/>
+    <sheet name="lr_0.0021" sheetId="21" r:id="rId21"/>
+    <sheet name="lr_0.0022" sheetId="22" r:id="rId22"/>
+    <sheet name="lr_0.0023" sheetId="23" r:id="rId23"/>
+    <sheet name="lr_0.0024" sheetId="24" r:id="rId24"/>
+    <sheet name="lr_0.0025" sheetId="25" r:id="rId25"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="1">
   <si>
     <t>window_size</t>
   </si>
@@ -37,8 +46,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,15 +61,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -99,34 +99,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office 2007–2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +155,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office 2007–2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +189,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +223,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office 2007–2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,11 +398,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,87 +422,87 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.13166666666666671</v>
+        <v>0.1316666666666667</v>
       </c>
       <c r="C2">
-        <v>0.14166666666666669</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="D2">
-        <v>0.15833333333333341</v>
+        <v>0.1583333333333334</v>
       </c>
       <c r="E2">
         <v>0.1866666666666667</v>
       </c>
       <c r="F2">
-        <v>0.25666666666666671</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.2566666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.12333333333333329</v>
+        <v>0.1233333333333333</v>
       </c>
       <c r="C3">
         <v>0.22</v>
       </c>
       <c r="D3">
-        <v>0.26166666666666671</v>
+        <v>0.2616666666666667</v>
       </c>
       <c r="E3">
-        <v>0.33666666666666673</v>
+        <v>0.3366666666666667</v>
       </c>
       <c r="F3">
-        <v>0.37333333333333341</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.3733333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.15666666666666659</v>
+        <v>0.1566666666666666</v>
       </c>
       <c r="C4">
-        <v>0.26666666666666672</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D4">
-        <v>0.32833333333333331</v>
+        <v>0.3283333333333333</v>
       </c>
       <c r="E4">
-        <v>0.39500000000000002</v>
+        <v>0.395</v>
       </c>
       <c r="F4">
-        <v>0.48666666666666658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.4866666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="C5">
-        <v>0.26833333333333331</v>
+        <v>0.2683333333333333</v>
       </c>
       <c r="D5">
-        <v>0.40833333333333338</v>
+        <v>0.4083333333333334</v>
       </c>
       <c r="E5">
-        <v>0.53166666666666662</v>
+        <v>0.5316666666666666</v>
       </c>
       <c r="F5">
-        <v>0.58833333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5883333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
@@ -521,7 +510,7 @@
         <v>0.23</v>
       </c>
       <c r="C6">
-        <v>0.37333333333333341</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="D6">
         <v>0.51</v>
@@ -533,7 +522,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -541,47 +530,47 @@
         <v>0.255</v>
       </c>
       <c r="C7">
-        <v>0.40166666666666673</v>
+        <v>0.4016666666666667</v>
       </c>
       <c r="D7">
-        <v>0.59500000000000008</v>
+        <v>0.5950000000000001</v>
       </c>
       <c r="E7">
-        <v>0.64666666666666661</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="F7">
-        <v>0.72333333333333327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7233333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.27666666666666673</v>
+        <v>0.2766666666666667</v>
       </c>
       <c r="C8">
         <v>0.5</v>
       </c>
       <c r="D8">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="E8">
-        <v>0.69666666666666666</v>
+        <v>0.6966666666666667</v>
       </c>
       <c r="F8">
-        <v>0.73499999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.735</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.33666666666666673</v>
+        <v>0.3366666666666667</v>
       </c>
       <c r="C9">
-        <v>0.54500000000000004</v>
+        <v>0.545</v>
       </c>
       <c r="D9">
         <v>0.65</v>
@@ -593,24 +582,35 @@
         <v>0.755</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.33333333333333331</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C10">
-        <v>0.59333333333333327</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="D10">
-        <v>0.72666666666666668</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="E10">
-        <v>0.75166666666666659</v>
-      </c>
-      <c r="F10" s="3">
+        <v>0.7516666666666666</v>
+      </c>
+      <c r="F10">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -619,11 +619,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,72 +643,72 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.13666666666666669</v>
+        <v>0.1366666666666667</v>
       </c>
       <c r="C2">
-        <v>0.43166666666666659</v>
+        <v>0.4316666666666666</v>
       </c>
       <c r="D2">
-        <v>0.64833333333333332</v>
+        <v>0.6483333333333333</v>
       </c>
       <c r="E2">
-        <v>0.72833333333333339</v>
+        <v>0.7283333333333334</v>
       </c>
       <c r="F2">
         <v>0.7533333333333333</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.47499999999999998</v>
+        <v>0.475</v>
       </c>
       <c r="C3">
         <v>0.77</v>
       </c>
       <c r="D3">
-        <v>0.81666666666666676</v>
+        <v>0.8166666666666668</v>
       </c>
       <c r="E3">
         <v>0.83</v>
       </c>
       <c r="F3">
-        <v>0.85333333333333339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8533333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.72333333333333327</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="C4">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D4">
-        <v>0.87333333333333341</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="E4">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="F4">
-        <v>0.90666666666666673</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9066666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.76333333333333331</v>
+        <v>0.7633333333333333</v>
       </c>
       <c r="C5">
         <v>0.8716666666666667</v>
@@ -717,53 +717,53 @@
         <v>0.91</v>
       </c>
       <c r="E5">
-        <v>0.91666666666666663</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F5">
         <v>0.91</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.81333333333333335</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C6">
         <v>0.9</v>
       </c>
       <c r="D6">
-        <v>0.90833333333333333</v>
+        <v>0.9083333333333333</v>
       </c>
       <c r="E6">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F6">
-        <v>0.94499999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.945</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="C7">
         <v>0.92</v>
       </c>
       <c r="D7">
-        <v>0.92500000000000016</v>
+        <v>0.9250000000000002</v>
       </c>
       <c r="E7">
-        <v>0.93166666666666664</v>
+        <v>0.9316666666666666</v>
       </c>
       <c r="F7">
-        <v>0.93166666666666664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9316666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
@@ -771,19 +771,19 @@
         <v>0.84</v>
       </c>
       <c r="C8">
-        <v>0.91166666666666674</v>
+        <v>0.9116666666666667</v>
       </c>
       <c r="D8">
-        <v>0.93833333333333335</v>
+        <v>0.9383333333333334</v>
       </c>
       <c r="E8">
-        <v>0.93833333333333335</v>
+        <v>0.9383333333333334</v>
       </c>
       <c r="F8">
-        <v>0.94333333333333336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9433333333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -791,36 +791,1940 @@
         <v>0.88</v>
       </c>
       <c r="C9">
-        <v>0.94499999999999995</v>
+        <v>0.945</v>
       </c>
       <c r="D9">
-        <v>0.93499999999999994</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="E9">
-        <v>0.94333333333333336</v>
+        <v>0.9433333333333334</v>
       </c>
       <c r="F9">
-        <v>0.95000000000000007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9500000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.88833333333333331</v>
+        <v>0.8883333333333333</v>
       </c>
       <c r="C10">
-        <v>0.92499999999999993</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="D10">
-        <v>0.94833333333333325</v>
+        <v>0.9483333333333333</v>
       </c>
       <c r="E10">
-        <v>0.95333333333333325</v>
+        <v>0.9533333333333333</v>
       </c>
       <c r="F10" s="2">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.9433333333333334</v>
+      </c>
+      <c r="E11">
+        <v>0.955</v>
+      </c>
+      <c r="F11">
+        <v>0.9483333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.17</v>
+      </c>
+      <c r="C2">
+        <v>0.4466666666666666</v>
+      </c>
+      <c r="D2">
+        <v>0.6816666666666666</v>
+      </c>
+      <c r="E2">
+        <v>0.7383333333333333</v>
+      </c>
+      <c r="F2">
+        <v>0.7666666666666666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.4616666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.7683333333333334</v>
+      </c>
+      <c r="D3">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E3">
+        <v>0.8483333333333333</v>
+      </c>
+      <c r="F3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.7283333333333334</v>
+      </c>
+      <c r="C4">
+        <v>0.8616666666666667</v>
+      </c>
+      <c r="D4">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.89</v>
+      </c>
+      <c r="F4">
+        <v>0.8966666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.79</v>
+      </c>
+      <c r="C5">
+        <v>0.8883333333333333</v>
+      </c>
+      <c r="D5">
+        <v>0.8850000000000001</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="F5">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.485</v>
+      </c>
+      <c r="C6">
+        <v>0.65</v>
+      </c>
+      <c r="D6">
+        <v>0.7233333333333333</v>
+      </c>
+      <c r="E6">
+        <v>0.7516666666666666</v>
+      </c>
+      <c r="F6">
+        <v>0.7866666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5216666666666666</v>
+      </c>
+      <c r="C7">
+        <v>0.6133333333333334</v>
+      </c>
+      <c r="D7">
+        <v>0.6616666666666666</v>
+      </c>
+      <c r="E7">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="F7">
+        <v>0.7783333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="C8">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="D8">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E8">
+        <v>0.745</v>
+      </c>
+      <c r="F8">
+        <v>0.7633333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.4566666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.6366666666666666</v>
+      </c>
+      <c r="D9">
+        <v>0.7366666666666667</v>
+      </c>
+      <c r="E9">
+        <v>0.7383333333333333</v>
+      </c>
+      <c r="F9">
+        <v>0.785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.4566666666666667</v>
+      </c>
+      <c r="C10">
+        <v>0.6466666666666666</v>
+      </c>
+      <c r="D10">
+        <v>0.68</v>
+      </c>
+      <c r="E10">
+        <v>0.755</v>
+      </c>
+      <c r="F10">
+        <v>0.785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1433333333333333</v>
+      </c>
+      <c r="C2">
+        <v>0.5033333333333333</v>
+      </c>
+      <c r="D2">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="E2">
+        <v>0.7733333333333334</v>
+      </c>
+      <c r="F2">
+        <v>0.8166666666666668</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="C3">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="D3">
+        <v>0.8450000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="F3">
+        <v>0.8966666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.725</v>
+      </c>
+      <c r="C4">
+        <v>0.83</v>
+      </c>
+      <c r="D4">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.8966666666666666</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8083333333333332</v>
+      </c>
+      <c r="C5">
+        <v>0.895</v>
+      </c>
+      <c r="D5">
+        <v>0.9033333333333333</v>
+      </c>
+      <c r="E5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="F5">
+        <v>0.9216666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="C6">
+        <v>0.6783333333333333</v>
+      </c>
+      <c r="D6">
+        <v>0.6966666666666667</v>
+      </c>
+      <c r="E6">
+        <v>0.7533333333333333</v>
+      </c>
+      <c r="F6">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5733333333333334</v>
+      </c>
+      <c r="C7">
+        <v>0.5616666666666666</v>
+      </c>
+      <c r="D7">
+        <v>0.6816666666666666</v>
+      </c>
+      <c r="E7">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F7">
+        <v>0.7799999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.4833333333333333</v>
+      </c>
+      <c r="C8">
+        <v>0.6366666666666667</v>
+      </c>
+      <c r="D8">
+        <v>0.7433333333333333</v>
+      </c>
+      <c r="E8">
+        <v>0.73</v>
+      </c>
+      <c r="F8">
+        <v>0.7999999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.4866666666666666</v>
+      </c>
+      <c r="C9">
+        <v>0.6233333333333334</v>
+      </c>
+      <c r="D9">
+        <v>0.7016666666666667</v>
+      </c>
+      <c r="E9">
+        <v>0.77</v>
+      </c>
+      <c r="F9">
+        <v>0.7600000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.4916666666666667</v>
+      </c>
+      <c r="C10">
+        <v>0.6833333333333332</v>
+      </c>
+      <c r="D10">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.745</v>
+      </c>
+      <c r="F10">
+        <v>0.7949999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1183333333333333</v>
+      </c>
+      <c r="C2">
+        <v>0.54</v>
+      </c>
+      <c r="D2">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E2">
+        <v>0.7533333333333333</v>
+      </c>
+      <c r="F2">
+        <v>0.785</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.8016666666666667</v>
+      </c>
+      <c r="D3">
+        <v>0.8616666666666667</v>
+      </c>
+      <c r="E3">
+        <v>0.87</v>
+      </c>
+      <c r="F3">
+        <v>0.8916666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.755</v>
+      </c>
+      <c r="C4">
+        <v>0.8466666666666667</v>
+      </c>
+      <c r="D4">
+        <v>0.8766666666666666</v>
+      </c>
+      <c r="E4">
+        <v>0.8883333333333333</v>
+      </c>
+      <c r="F4">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="C5">
+        <v>0.89</v>
+      </c>
+      <c r="D5">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="E5">
+        <v>0.93</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9333333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5216666666666666</v>
+      </c>
+      <c r="C6">
+        <v>0.61</v>
+      </c>
+      <c r="D6">
+        <v>0.7283333333333334</v>
+      </c>
+      <c r="E6">
+        <v>0.7816666666666667</v>
+      </c>
+      <c r="F6">
+        <v>0.7966666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.4533333333333334</v>
+      </c>
+      <c r="C7">
+        <v>0.6549999999999999</v>
+      </c>
+      <c r="D7">
+        <v>0.7616666666666667</v>
+      </c>
+      <c r="E7">
+        <v>0.7733333333333334</v>
+      </c>
+      <c r="F7">
+        <v>0.8016666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.5399999999999999</v>
+      </c>
+      <c r="C8">
+        <v>0.6716666666666667</v>
+      </c>
+      <c r="D8">
+        <v>0.7166666666666667</v>
+      </c>
+      <c r="E8">
+        <v>0.7616666666666667</v>
+      </c>
+      <c r="F8">
+        <v>0.7933333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.4116666666666666</v>
+      </c>
+      <c r="C9">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.6833333333333332</v>
+      </c>
+      <c r="E9">
+        <v>0.7633333333333333</v>
+      </c>
+      <c r="F9">
+        <v>0.8083333333333332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.545</v>
+      </c>
+      <c r="C10">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="D10">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="E10">
+        <v>0.77</v>
+      </c>
+      <c r="F10">
+        <v>0.7799999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.145</v>
+      </c>
+      <c r="C2">
+        <v>0.5533333333333333</v>
+      </c>
+      <c r="D2">
+        <v>0.7816666666666667</v>
+      </c>
+      <c r="E2">
+        <v>0.7866666666666667</v>
+      </c>
+      <c r="F2">
+        <v>0.8083333333333332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.5316666666666666</v>
+      </c>
+      <c r="C3">
+        <v>0.805</v>
+      </c>
+      <c r="D3">
+        <v>0.86</v>
+      </c>
+      <c r="E3">
+        <v>0.8649999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.8850000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="C4">
+        <v>0.85</v>
+      </c>
+      <c r="D4">
+        <v>0.9</v>
+      </c>
+      <c r="E4">
+        <v>0.9116666666666667</v>
+      </c>
+      <c r="F4">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.835</v>
+      </c>
+      <c r="C5">
+        <v>0.9066666666666667</v>
+      </c>
+      <c r="D5">
+        <v>0.91</v>
+      </c>
+      <c r="E5">
+        <v>0.93</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9333333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5033333333333333</v>
+      </c>
+      <c r="C6">
+        <v>0.66</v>
+      </c>
+      <c r="D6">
+        <v>0.7283333333333334</v>
+      </c>
+      <c r="E6">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5483333333333333</v>
+      </c>
+      <c r="C7">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="D7">
+        <v>0.6933333333333334</v>
+      </c>
+      <c r="E7">
+        <v>0.77</v>
+      </c>
+      <c r="F7">
+        <v>0.8233333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.545</v>
+      </c>
+      <c r="C8">
+        <v>0.6533333333333333</v>
+      </c>
+      <c r="D8">
+        <v>0.7366666666666667</v>
+      </c>
+      <c r="E8">
+        <v>0.755</v>
+      </c>
+      <c r="F8">
+        <v>0.7999999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.4983333333333334</v>
+      </c>
+      <c r="C9">
+        <v>0.6483333333333333</v>
+      </c>
+      <c r="D9">
+        <v>0.765</v>
+      </c>
+      <c r="E9">
+        <v>0.79</v>
+      </c>
+      <c r="F9">
+        <v>0.7933333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5133333333333333</v>
+      </c>
+      <c r="C10">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="D10">
+        <v>0.7283333333333334</v>
+      </c>
+      <c r="E10">
+        <v>0.7733333333333334</v>
+      </c>
+      <c r="F10">
+        <v>0.7999999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.13</v>
+      </c>
+      <c r="C2">
+        <v>0.52</v>
+      </c>
+      <c r="D2">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="E2">
+        <v>0.8033333333333333</v>
+      </c>
+      <c r="F2">
+        <v>0.8033333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.8099999999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.8583333333333334</v>
+      </c>
+      <c r="E3">
+        <v>0.87</v>
+      </c>
+      <c r="F3">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.7983333333333333</v>
+      </c>
+      <c r="C4">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="D4">
+        <v>0.9066666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.9016666666666667</v>
+      </c>
+      <c r="F4">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="C5">
+        <v>0.8866666666666667</v>
+      </c>
+      <c r="D5">
+        <v>0.9183333333333333</v>
+      </c>
+      <c r="E5">
+        <v>0.9283333333333333</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9466666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.545</v>
+      </c>
+      <c r="C6">
+        <v>0.6533333333333333</v>
+      </c>
+      <c r="D6">
+        <v>0.765</v>
+      </c>
+      <c r="E6">
+        <v>0.7683333333333334</v>
+      </c>
+      <c r="F6">
+        <v>0.8233333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5816666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.6683333333333333</v>
+      </c>
+      <c r="D7">
+        <v>0.75</v>
+      </c>
+      <c r="E7">
+        <v>0.7983333333333333</v>
+      </c>
+      <c r="F7">
+        <v>0.8016666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.59</v>
+      </c>
+      <c r="C8">
+        <v>0.6616666666666667</v>
+      </c>
+      <c r="D8">
+        <v>0.7433333333333333</v>
+      </c>
+      <c r="E8">
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="F8">
+        <v>0.8133333333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.605</v>
+      </c>
+      <c r="C9">
+        <v>0.6883333333333334</v>
+      </c>
+      <c r="D9">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="E9">
+        <v>0.7716666666666666</v>
+      </c>
+      <c r="F9">
+        <v>0.8283333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="C10">
+        <v>0.6533333333333333</v>
+      </c>
+      <c r="D10">
+        <v>0.73</v>
+      </c>
+      <c r="E10">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="F10">
+        <v>0.7966666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1816666666666666</v>
+      </c>
+      <c r="C2">
+        <v>0.5766666666666667</v>
+      </c>
+      <c r="D2">
+        <v>0.79</v>
+      </c>
+      <c r="E2">
+        <v>0.8150000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.585</v>
+      </c>
+      <c r="C3">
+        <v>0.8466666666666667</v>
+      </c>
+      <c r="D3">
+        <v>0.8716666666666667</v>
+      </c>
+      <c r="E3">
+        <v>0.8916666666666666</v>
+      </c>
+      <c r="F3">
+        <v>0.8916666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.7933333333333333</v>
+      </c>
+      <c r="C4">
+        <v>0.8916666666666666</v>
+      </c>
+      <c r="D4">
+        <v>0.915</v>
+      </c>
+      <c r="E4">
+        <v>0.9316666666666666</v>
+      </c>
+      <c r="F4">
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8649999999999999</v>
+      </c>
+      <c r="C5">
+        <v>0.9083333333333333</v>
+      </c>
+      <c r="D5">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="E5">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5616666666666666</v>
+      </c>
+      <c r="C6">
+        <v>0.67</v>
+      </c>
+      <c r="D6">
+        <v>0.7433333333333333</v>
+      </c>
+      <c r="E6">
+        <v>0.7966666666666667</v>
+      </c>
+      <c r="F6">
+        <v>0.8300000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.6116666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.6816666666666666</v>
+      </c>
+      <c r="D7">
+        <v>0.725</v>
+      </c>
+      <c r="E7">
+        <v>0.795</v>
+      </c>
+      <c r="F7">
+        <v>0.8099999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.535</v>
+      </c>
+      <c r="C8">
+        <v>0.6916666666666668</v>
+      </c>
+      <c r="D8">
+        <v>0.745</v>
+      </c>
+      <c r="E8">
+        <v>0.7616666666666667</v>
+      </c>
+      <c r="F8">
+        <v>0.8283333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="C9">
+        <v>0.6716666666666667</v>
+      </c>
+      <c r="D9">
+        <v>0.765</v>
+      </c>
+      <c r="E9">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.6133333333333333</v>
+      </c>
+      <c r="C10">
+        <v>0.6983333333333334</v>
+      </c>
+      <c r="D10">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="E10">
+        <v>0.7766666666666667</v>
+      </c>
+      <c r="F10">
+        <v>0.8116666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="C2">
+        <v>0.59</v>
+      </c>
+      <c r="D2">
+        <v>0.77</v>
+      </c>
+      <c r="E2">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="F2">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.5966666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.8616666666666667</v>
+      </c>
+      <c r="D3">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E3">
+        <v>0.8933333333333334</v>
+      </c>
+      <c r="F3">
+        <v>0.9116666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C4">
+        <v>0.8883333333333333</v>
+      </c>
+      <c r="D4">
+        <v>0.9033333333333333</v>
+      </c>
+      <c r="E4">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="F4">
+        <v>0.915</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8483333333333333</v>
+      </c>
+      <c r="C5">
+        <v>0.895</v>
+      </c>
+      <c r="D5">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.9383333333333334</v>
+      </c>
+      <c r="F5">
+        <v>0.9366666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.545</v>
+      </c>
+      <c r="C6">
+        <v>0.6833333333333332</v>
+      </c>
+      <c r="D6">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="E6">
+        <v>0.805</v>
+      </c>
+      <c r="F6">
+        <v>0.8133333333333334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5166666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.6983333333333333</v>
+      </c>
+      <c r="D7">
+        <v>0.7366666666666667</v>
+      </c>
+      <c r="E7">
+        <v>0.77</v>
+      </c>
+      <c r="F7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.625</v>
+      </c>
+      <c r="C8">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="D8">
+        <v>0.745</v>
+      </c>
+      <c r="E8">
+        <v>0.7933333333333333</v>
+      </c>
+      <c r="F8">
+        <v>0.8166666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.5966666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D9">
+        <v>0.7566666666666667</v>
+      </c>
+      <c r="E9">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.8166666666666668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.515</v>
+      </c>
+      <c r="C10">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D10">
+        <v>0.745</v>
+      </c>
+      <c r="E10">
+        <v>0.7966666666666667</v>
+      </c>
+      <c r="F10">
+        <v>0.8183333333333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.13</v>
+      </c>
+      <c r="C2">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="D2">
+        <v>0.7866666666666667</v>
+      </c>
+      <c r="E2">
+        <v>0.785</v>
+      </c>
+      <c r="F2">
+        <v>0.8366666666666666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.6516666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.8450000000000001</v>
+      </c>
+      <c r="D3">
+        <v>0.8466666666666667</v>
+      </c>
+      <c r="E3">
+        <v>0.8833333333333333</v>
+      </c>
+      <c r="F3">
+        <v>0.9049999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8116666666666666</v>
+      </c>
+      <c r="C4">
+        <v>0.88</v>
+      </c>
+      <c r="D4">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.9249999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.9250000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8566666666666666</v>
+      </c>
+      <c r="C5">
+        <v>0.9049999999999999</v>
+      </c>
+      <c r="D5">
+        <v>0.91</v>
+      </c>
+      <c r="E5">
+        <v>0.9249999999999999</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9466666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5916666666666667</v>
+      </c>
+      <c r="C6">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="D6">
+        <v>0.7633333333333333</v>
+      </c>
+      <c r="E6">
+        <v>0.79</v>
+      </c>
+      <c r="F6">
+        <v>0.8416666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.585</v>
+      </c>
+      <c r="C7">
+        <v>0.7050000000000001</v>
+      </c>
+      <c r="D7">
+        <v>0.7716666666666666</v>
+      </c>
+      <c r="E7">
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="F7">
+        <v>0.8283333333333333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.61</v>
+      </c>
+      <c r="C8">
+        <v>0.6483333333333333</v>
+      </c>
+      <c r="D8">
+        <v>0.7716666666666666</v>
+      </c>
+      <c r="E8">
+        <v>0.8216666666666667</v>
+      </c>
+      <c r="F8">
+        <v>0.8183333333333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.6516666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.7316666666666666</v>
+      </c>
+      <c r="D9">
+        <v>0.785</v>
+      </c>
+      <c r="E9">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="F9">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5983333333333333</v>
+      </c>
+      <c r="C10">
+        <v>0.6916666666666668</v>
+      </c>
+      <c r="D10">
+        <v>0.7633333333333333</v>
+      </c>
+      <c r="E10">
+        <v>0.8083333333333332</v>
+      </c>
+      <c r="F10">
+        <v>0.8250000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1483333333333333</v>
+      </c>
+      <c r="C2">
+        <v>0.6283333333333333</v>
+      </c>
+      <c r="D2">
+        <v>0.7966666666666667</v>
+      </c>
+      <c r="E2">
+        <v>0.83</v>
+      </c>
+      <c r="F2">
+        <v>0.8383333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="C3">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="D3">
+        <v>0.8850000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.8916666666666666</v>
+      </c>
+      <c r="F3">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8316666666666667</v>
+      </c>
+      <c r="C4">
+        <v>0.8783333333333333</v>
+      </c>
+      <c r="D4">
+        <v>0.9366666666666666</v>
+      </c>
+      <c r="E4">
+        <v>0.92</v>
+      </c>
+      <c r="F4">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8633333333333333</v>
+      </c>
+      <c r="C5">
+        <v>0.91</v>
+      </c>
+      <c r="D5">
+        <v>0.9266666666666667</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9466666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5516666666666666</v>
+      </c>
+      <c r="C6">
+        <v>0.6966666666666667</v>
+      </c>
+      <c r="D6">
+        <v>0.7566666666666667</v>
+      </c>
+      <c r="E6">
+        <v>0.7883333333333334</v>
+      </c>
+      <c r="F6">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5866666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.735</v>
+      </c>
+      <c r="D7">
+        <v>0.7716666666666666</v>
+      </c>
+      <c r="E7">
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="F7">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.5216666666666666</v>
+      </c>
+      <c r="C8">
+        <v>0.695</v>
+      </c>
+      <c r="D8">
+        <v>0.755</v>
+      </c>
+      <c r="E8">
+        <v>0.8150000000000001</v>
+      </c>
+      <c r="F8">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="D9">
+        <v>0.77</v>
+      </c>
+      <c r="E9">
+        <v>0.8150000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.8283333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5750000000000001</v>
+      </c>
+      <c r="C10">
+        <v>0.6916666666666668</v>
+      </c>
+      <c r="D10">
+        <v>0.7266666666666667</v>
+      </c>
+      <c r="E10">
+        <v>0.8150000000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.8316666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +2733,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +2757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -864,96 +2768,96 @@
         <v>0.185</v>
       </c>
       <c r="D2">
-        <v>0.23499999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="E2">
-        <v>0.28333333333333338</v>
+        <v>0.2833333333333334</v>
       </c>
       <c r="F2">
-        <v>0.35499999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="C3">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="D3">
-        <v>0.43333333333333329</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E3">
-        <v>0.51666666666666672</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="F3">
-        <v>0.56833333333333336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5683333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.25666666666666671</v>
+        <v>0.2566666666666667</v>
       </c>
       <c r="C4">
-        <v>0.39500000000000002</v>
+        <v>0.395</v>
       </c>
       <c r="D4">
-        <v>0.52833333333333332</v>
+        <v>0.5283333333333333</v>
       </c>
       <c r="E4">
-        <v>0.63500000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="F4">
-        <v>0.68500000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.6850000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.30833333333333329</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="C5">
-        <v>0.54833333333333334</v>
+        <v>0.5483333333333333</v>
       </c>
       <c r="D5">
         <v>0.64</v>
       </c>
       <c r="E5">
-        <v>0.71166666666666656</v>
+        <v>0.7116666666666666</v>
       </c>
       <c r="F5">
-        <v>0.75666666666666671</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7566666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.38166666666666671</v>
+        <v>0.3816666666666667</v>
       </c>
       <c r="C6">
         <v>0.6166666666666667</v>
       </c>
       <c r="D6">
-        <v>0.69499999999999995</v>
+        <v>0.695</v>
       </c>
       <c r="E6">
         <v>0.77</v>
       </c>
       <c r="F6">
-        <v>0.80500000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.805</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -961,7 +2865,7 @@
         <v>0.435</v>
       </c>
       <c r="C7">
-        <v>0.67666666666666675</v>
+        <v>0.6766666666666667</v>
       </c>
       <c r="D7">
         <v>0.7466666666666667</v>
@@ -970,30 +2874,30 @@
         <v>0.77</v>
       </c>
       <c r="F7">
-        <v>0.83166666666666667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8316666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.45333333333333331</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="C8">
-        <v>0.68666666666666665</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="D8">
-        <v>0.77833333333333332</v>
+        <v>0.7783333333333333</v>
       </c>
       <c r="E8">
-        <v>0.82500000000000007</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="F8">
         <v>0.85</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -1001,36 +2905,1307 @@
         <v>0.505</v>
       </c>
       <c r="C9">
-        <v>0.75166666666666659</v>
+        <v>0.7516666666666666</v>
       </c>
       <c r="D9">
         <v>0.83</v>
       </c>
       <c r="E9">
-        <v>0.84666666666666668</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="F9">
         <v>0.88</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.54333333333333333</v>
+        <v>0.5433333333333333</v>
       </c>
       <c r="C10">
-        <v>0.75166666666666659</v>
+        <v>0.7516666666666666</v>
       </c>
       <c r="D10">
         <v>0.83</v>
       </c>
       <c r="E10">
-        <v>0.87666666666666659</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.88500000000000012</v>
+        <v>0.8766666666666666</v>
+      </c>
+      <c r="F10">
+        <v>0.8850000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0.8716666666666667</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.9016666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1283333333333333</v>
+      </c>
+      <c r="C2">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="D2">
+        <v>0.795</v>
+      </c>
+      <c r="E2">
+        <v>0.8383333333333334</v>
+      </c>
+      <c r="F2">
+        <v>0.8450000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="D3">
+        <v>0.8916666666666666</v>
+      </c>
+      <c r="E3">
+        <v>0.8983333333333334</v>
+      </c>
+      <c r="F3">
+        <v>0.9116666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8483333333333333</v>
+      </c>
+      <c r="C4">
+        <v>0.9066666666666667</v>
+      </c>
+      <c r="D4">
+        <v>0.9016666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.9349999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8850000000000001</v>
+      </c>
+      <c r="C5">
+        <v>0.92</v>
+      </c>
+      <c r="D5">
+        <v>0.9283333333333333</v>
+      </c>
+      <c r="E5">
+        <v>0.9416666666666668</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9483333333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5866666666666667</v>
+      </c>
+      <c r="C6">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="D6">
+        <v>0.7566666666666667</v>
+      </c>
+      <c r="E6">
+        <v>0.8083333333333332</v>
+      </c>
+      <c r="F6">
+        <v>0.8450000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.6716666666666667</v>
+      </c>
+      <c r="D7">
+        <v>0.785</v>
+      </c>
+      <c r="E7">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.8316666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="C8">
+        <v>0.6816666666666666</v>
+      </c>
+      <c r="D8">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="E8">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.8366666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.5616666666666666</v>
+      </c>
+      <c r="C9">
+        <v>0.7316666666666666</v>
+      </c>
+      <c r="D9">
+        <v>0.7783333333333333</v>
+      </c>
+      <c r="E9">
+        <v>0.82</v>
+      </c>
+      <c r="F9">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5533333333333333</v>
+      </c>
+      <c r="C10">
+        <v>0.7050000000000001</v>
+      </c>
+      <c r="D10">
+        <v>0.7533333333333333</v>
+      </c>
+      <c r="E10">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F10">
+        <v>0.82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1583333333333333</v>
+      </c>
+      <c r="C2">
+        <v>0.6316666666666667</v>
+      </c>
+      <c r="D2">
+        <v>0.8083333333333332</v>
+      </c>
+      <c r="E2">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="F2">
+        <v>0.8433333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.6616666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.8783333333333333</v>
+      </c>
+      <c r="D3">
+        <v>0.8966666666666666</v>
+      </c>
+      <c r="E3">
+        <v>0.8883333333333333</v>
+      </c>
+      <c r="F3">
+        <v>0.9116666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8233333333333333</v>
+      </c>
+      <c r="C4">
+        <v>0.9083333333333333</v>
+      </c>
+      <c r="D4">
+        <v>0.9183333333333333</v>
+      </c>
+      <c r="E4">
+        <v>0.9183333333333333</v>
+      </c>
+      <c r="F4">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8783333333333333</v>
+      </c>
+      <c r="C5">
+        <v>0.9116666666666666</v>
+      </c>
+      <c r="D5">
+        <v>0.9383333333333334</v>
+      </c>
+      <c r="E5">
+        <v>0.9416666666666668</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9583333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5466666666666667</v>
+      </c>
+      <c r="C6">
+        <v>0.73</v>
+      </c>
+      <c r="D6">
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="E6">
+        <v>0.82</v>
+      </c>
+      <c r="F6">
+        <v>0.8516666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.6133333333333333</v>
+      </c>
+      <c r="C7">
+        <v>0.7366666666666667</v>
+      </c>
+      <c r="D7">
+        <v>0.7766666666666667</v>
+      </c>
+      <c r="E7">
+        <v>0.8183333333333334</v>
+      </c>
+      <c r="F7">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.6316666666666667</v>
+      </c>
+      <c r="C8">
+        <v>0.7116666666666666</v>
+      </c>
+      <c r="D8">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E8">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="F8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="D9">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="E9">
+        <v>0.8099999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.6216666666666667</v>
+      </c>
+      <c r="C10">
+        <v>0.7050000000000001</v>
+      </c>
+      <c r="D10">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E10">
+        <v>0.8183333333333334</v>
+      </c>
+      <c r="F10">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1316666666666667</v>
+      </c>
+      <c r="C2">
+        <v>0.6966666666666667</v>
+      </c>
+      <c r="D2">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E2">
+        <v>0.84</v>
+      </c>
+      <c r="F2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.64</v>
+      </c>
+      <c r="C3">
+        <v>0.8783333333333333</v>
+      </c>
+      <c r="D3">
+        <v>0.8933333333333334</v>
+      </c>
+      <c r="E3">
+        <v>0.9133333333333334</v>
+      </c>
+      <c r="F3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C4">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="D4">
+        <v>0.915</v>
+      </c>
+      <c r="E4">
+        <v>0.9249999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.9316666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8716666666666667</v>
+      </c>
+      <c r="C5">
+        <v>0.9116666666666667</v>
+      </c>
+      <c r="D5">
+        <v>0.9333333333333335</v>
+      </c>
+      <c r="E5">
+        <v>0.9366666666666666</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.9383333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.6266666666666666</v>
+      </c>
+      <c r="C6">
+        <v>0.745</v>
+      </c>
+      <c r="D6">
+        <v>0.775</v>
+      </c>
+      <c r="E6">
+        <v>0.8216666666666667</v>
+      </c>
+      <c r="F6">
+        <v>0.8433333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="C7">
+        <v>0.71</v>
+      </c>
+      <c r="D7">
+        <v>0.7933333333333333</v>
+      </c>
+      <c r="E7">
+        <v>0.82</v>
+      </c>
+      <c r="F7">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.6033333333333334</v>
+      </c>
+      <c r="C8">
+        <v>0.7116666666666666</v>
+      </c>
+      <c r="D8">
+        <v>0.7816666666666666</v>
+      </c>
+      <c r="E8">
+        <v>0.8183333333333334</v>
+      </c>
+      <c r="F8">
+        <v>0.8366666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.6183333333333333</v>
+      </c>
+      <c r="C9">
+        <v>0.7399999999999999</v>
+      </c>
+      <c r="D9">
+        <v>0.7983333333333333</v>
+      </c>
+      <c r="E9">
+        <v>0.8216666666666667</v>
+      </c>
+      <c r="F9">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.6216666666666667</v>
+      </c>
+      <c r="C10">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="D10">
+        <v>0.7716666666666666</v>
+      </c>
+      <c r="E10">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F10">
+        <v>0.8383333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1616666666666667</v>
+      </c>
+      <c r="C2">
+        <v>0.665</v>
+      </c>
+      <c r="D2">
+        <v>0.8249999999999998</v>
+      </c>
+      <c r="E2">
+        <v>0.86</v>
+      </c>
+      <c r="F2">
+        <v>0.8633333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="C3">
+        <v>0.87</v>
+      </c>
+      <c r="D3">
+        <v>0.8916666666666666</v>
+      </c>
+      <c r="E3">
+        <v>0.9116666666666667</v>
+      </c>
+      <c r="F3">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8450000000000001</v>
+      </c>
+      <c r="C4">
+        <v>0.8983333333333334</v>
+      </c>
+      <c r="D4">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.9383333333333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8716666666666667</v>
+      </c>
+      <c r="C5">
+        <v>0.92</v>
+      </c>
+      <c r="D5">
+        <v>0.9383333333333334</v>
+      </c>
+      <c r="E5">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.945</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.6133333333333333</v>
+      </c>
+      <c r="C6">
+        <v>0.71</v>
+      </c>
+      <c r="D6">
+        <v>0.7816666666666667</v>
+      </c>
+      <c r="E6">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.8216666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.6883333333333334</v>
+      </c>
+      <c r="D7">
+        <v>0.795</v>
+      </c>
+      <c r="E7">
+        <v>0.8099999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.8416666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.6033333333333334</v>
+      </c>
+      <c r="C8">
+        <v>0.7383333333333333</v>
+      </c>
+      <c r="D8">
+        <v>0.7949999999999999</v>
+      </c>
+      <c r="E8">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="F8">
+        <v>0.8316666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="D9">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F9">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5366666666666666</v>
+      </c>
+      <c r="C10">
+        <v>0.6783333333333333</v>
+      </c>
+      <c r="D10">
+        <v>0.7883333333333334</v>
+      </c>
+      <c r="E10">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="F10">
+        <v>0.83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.14</v>
+      </c>
+      <c r="C2">
+        <v>0.6883333333333334</v>
+      </c>
+      <c r="D2">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E2">
+        <v>0.8616666666666667</v>
+      </c>
+      <c r="F2">
+        <v>0.8316666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.7016666666666667</v>
+      </c>
+      <c r="C3">
+        <v>0.87</v>
+      </c>
+      <c r="D3">
+        <v>0.9033333333333333</v>
+      </c>
+      <c r="E3">
+        <v>0.9049999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.9216666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.86</v>
+      </c>
+      <c r="C4">
+        <v>0.9</v>
+      </c>
+      <c r="D4">
+        <v>0.9266666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.9283333333333333</v>
+      </c>
+      <c r="F4">
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.8850000000000001</v>
+      </c>
+      <c r="C5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="D5">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.9416666666666668</v>
+      </c>
+      <c r="F5">
+        <v>0.9400000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.625</v>
+      </c>
+      <c r="C6">
+        <v>0.725</v>
+      </c>
+      <c r="D6">
+        <v>0.785</v>
+      </c>
+      <c r="E6">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F6">
+        <v>0.8216666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.6783333333333333</v>
+      </c>
+      <c r="C7">
+        <v>0.66</v>
+      </c>
+      <c r="D7">
+        <v>0.7783333333333333</v>
+      </c>
+      <c r="E7">
+        <v>0.8366666666666666</v>
+      </c>
+      <c r="F7">
+        <v>0.8183333333333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.595</v>
+      </c>
+      <c r="C8">
+        <v>0.735</v>
+      </c>
+      <c r="D8">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E8">
+        <v>0.8466666666666667</v>
+      </c>
+      <c r="F8">
+        <v>0.805</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C9">
+        <v>0.7266666666666666</v>
+      </c>
+      <c r="D9">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="E9">
+        <v>0.83</v>
+      </c>
+      <c r="F9">
+        <v>0.8099999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.5983333333333333</v>
+      </c>
+      <c r="C10">
+        <v>0.715</v>
+      </c>
+      <c r="D10">
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="E10">
+        <v>0.8216666666666667</v>
+      </c>
+      <c r="F10">
+        <v>0.79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0.1516666666666667</v>
+      </c>
+      <c r="C2">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D2">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="E2">
+        <v>0.8383333333333334</v>
+      </c>
+      <c r="F2">
+        <v>0.8516666666666666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.7050000000000001</v>
+      </c>
+      <c r="C3">
+        <v>0.9033333333333333</v>
+      </c>
+      <c r="D3">
+        <v>0.9016666666666667</v>
+      </c>
+      <c r="E3">
+        <v>0.9250000000000002</v>
+      </c>
+      <c r="F3">
+        <v>0.9266666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.8616666666666667</v>
+      </c>
+      <c r="C4">
+        <v>0.9283333333333333</v>
+      </c>
+      <c r="D4">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="E4">
+        <v>0.93</v>
+      </c>
+      <c r="F4">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.915</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.9416666666666668</v>
+      </c>
+      <c r="D5">
+        <v>0.9266666666666667</v>
+      </c>
+      <c r="E5">
+        <v>0.93</v>
+      </c>
+      <c r="F5">
+        <v>0.9383333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>0.5750000000000001</v>
+      </c>
+      <c r="C6">
+        <v>0.765</v>
+      </c>
+      <c r="D6">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="E6">
+        <v>0.8316666666666667</v>
+      </c>
+      <c r="F6">
+        <v>0.8266666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.6016666666666667</v>
+      </c>
+      <c r="C7">
+        <v>0.745</v>
+      </c>
+      <c r="D7">
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="E7">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="F7">
+        <v>0.805</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>0.5983333333333333</v>
+      </c>
+      <c r="C8">
+        <v>0.7483333333333334</v>
+      </c>
+      <c r="D8">
+        <v>0.79</v>
+      </c>
+      <c r="E8">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="F8">
+        <v>0.7933333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.5933333333333334</v>
+      </c>
+      <c r="C9">
+        <v>0.715</v>
+      </c>
+      <c r="D9">
+        <v>0.7883333333333334</v>
+      </c>
+      <c r="E9">
+        <v>0.8216666666666667</v>
+      </c>
+      <c r="F9">
+        <v>0.8116666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0.625</v>
+      </c>
+      <c r="C10">
+        <v>0.7366666666666667</v>
+      </c>
+      <c r="D10">
+        <v>0.7783333333333333</v>
+      </c>
+      <c r="E10">
+        <v>0.8483333333333333</v>
+      </c>
+      <c r="F10">
+        <v>0.8250000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1039,11 +4214,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +4238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1071,19 +4246,19 @@
         <v>0.1033333333333333</v>
       </c>
       <c r="C2">
-        <v>0.19500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="D2">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="E2">
-        <v>0.40166666666666673</v>
+        <v>0.4016666666666667</v>
       </c>
       <c r="F2">
         <v>0.47</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -1094,153 +4269,164 @@
         <v>0.44</v>
       </c>
       <c r="D3">
-        <v>0.53500000000000003</v>
+        <v>0.535</v>
       </c>
       <c r="E3">
-        <v>0.61333333333333329</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F3">
-        <v>0.69333333333333336</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.6933333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.37166666666666659</v>
+        <v>0.3716666666666666</v>
       </c>
       <c r="C4">
-        <v>0.54333333333333333</v>
+        <v>0.5433333333333333</v>
       </c>
       <c r="D4">
-        <v>0.67666666666666675</v>
+        <v>0.6766666666666667</v>
       </c>
       <c r="E4">
-        <v>0.72666666666666657</v>
+        <v>0.7266666666666666</v>
       </c>
       <c r="F4">
-        <v>0.79999999999999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7999999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.48166666666666658</v>
+        <v>0.4816666666666666</v>
       </c>
       <c r="C5">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>0.73999999999999988</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="E5">
-        <v>0.77999999999999992</v>
+        <v>0.7799999999999999</v>
       </c>
       <c r="F5">
-        <v>0.81333333333333335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8133333333333334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.51833333333333342</v>
+        <v>0.5183333333333334</v>
       </c>
       <c r="C6">
-        <v>0.72333333333333327</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="D6">
-        <v>0.78500000000000003</v>
+        <v>0.785</v>
       </c>
       <c r="E6">
         <v>0.84</v>
       </c>
       <c r="F6">
-        <v>0.85833333333333339</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8583333333333334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.57166666666666666</v>
+        <v>0.5716666666666667</v>
       </c>
       <c r="C7">
-        <v>0.75166666666666659</v>
+        <v>0.7516666666666666</v>
       </c>
       <c r="D7">
-        <v>0.82166666666666666</v>
+        <v>0.8216666666666667</v>
       </c>
       <c r="E7">
-        <v>0.86333333333333329</v>
+        <v>0.8633333333333333</v>
       </c>
       <c r="F7">
-        <v>0.88500000000000012</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8850000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.63166666666666671</v>
+        <v>0.6316666666666667</v>
       </c>
       <c r="C8">
-        <v>0.79333333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="D8">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="E8">
         <v>0.87</v>
       </c>
       <c r="F8">
-        <v>0.90166666666666673</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9016666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.63500000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="C9">
-        <v>0.82166666666666666</v>
+        <v>0.8216666666666667</v>
       </c>
       <c r="D9">
-        <v>0.86499999999999988</v>
+        <v>0.8649999999999999</v>
       </c>
       <c r="E9">
-        <v>0.88500000000000012</v>
+        <v>0.8850000000000001</v>
       </c>
       <c r="F9">
-        <v>0.89833333333333343</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8983333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.67333333333333334</v>
+        <v>0.6733333333333333</v>
       </c>
       <c r="C10">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D10">
         <v>0.875</v>
       </c>
       <c r="E10">
-        <v>0.90833333333333333</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.92333333333333334</v>
+        <v>0.9083333333333333</v>
+      </c>
+      <c r="F10">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0.8983333333333334</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.9283333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1249,11 +4435,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +4459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1281,19 +4467,19 @@
         <v>0.12</v>
       </c>
       <c r="C2">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="D2">
-        <v>0.36833333333333329</v>
+        <v>0.3683333333333333</v>
       </c>
       <c r="E2">
-        <v>0.48666666666666658</v>
+        <v>0.4866666666666666</v>
       </c>
       <c r="F2">
-        <v>0.52833333333333332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5283333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -1301,19 +4487,19 @@
         <v>0.26</v>
       </c>
       <c r="C3">
-        <v>0.54166666666666663</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D3">
-        <v>0.58166666666666667</v>
+        <v>0.5816666666666667</v>
       </c>
       <c r="E3">
-        <v>0.69000000000000006</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="F3">
         <v>0.7416666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -1321,19 +4507,19 @@
         <v>0.43</v>
       </c>
       <c r="C4">
-        <v>0.64833333333333332</v>
+        <v>0.6483333333333333</v>
       </c>
       <c r="D4">
         <v>0.7533333333333333</v>
       </c>
       <c r="E4">
-        <v>0.79333333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F4">
-        <v>0.82166666666666666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8216666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
@@ -1341,10 +4527,10 @@
         <v>0.48</v>
       </c>
       <c r="C5">
-        <v>0.71166666666666656</v>
+        <v>0.7116666666666666</v>
       </c>
       <c r="D5">
-        <v>0.81666666666666676</v>
+        <v>0.8166666666666668</v>
       </c>
       <c r="E5">
         <v>0.83</v>
@@ -1353,27 +4539,27 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.60333333333333339</v>
+        <v>0.6033333333333334</v>
       </c>
       <c r="C6">
-        <v>0.79333333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="D6">
-        <v>0.83499999999999996</v>
+        <v>0.835</v>
       </c>
       <c r="E6">
-        <v>0.86166666666666669</v>
+        <v>0.8616666666666667</v>
       </c>
       <c r="F6">
         <v>0.88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -1384,73 +4570,84 @@
         <v>0.79</v>
       </c>
       <c r="D7">
-        <v>0.83833333333333326</v>
+        <v>0.8383333333333333</v>
       </c>
       <c r="E7">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="F7">
-        <v>0.90166666666666673</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9016666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.71666666666666667</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="C8">
         <v>0.84</v>
       </c>
       <c r="D8">
-        <v>0.87333333333333341</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="E8">
         <v>0.9</v>
       </c>
       <c r="F8">
-        <v>0.91833333333333333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9183333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.72333333333333327</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="C9">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="D9">
         <v>0.9</v>
       </c>
       <c r="E9">
-        <v>0.91500000000000004</v>
+        <v>0.915</v>
       </c>
       <c r="F9">
-        <v>0.92333333333333334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.76000000000000012</v>
+        <v>0.7600000000000001</v>
       </c>
       <c r="C10">
         <v>0.8833333333333333</v>
       </c>
       <c r="D10">
-        <v>0.89833333333333343</v>
+        <v>0.8983333333333334</v>
       </c>
       <c r="E10">
-        <v>0.92500000000000016</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.93166666666666664</v>
+        <v>0.9250000000000002</v>
+      </c>
+      <c r="F10">
+        <v>0.9316666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.9516666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1459,11 +4656,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +4680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1491,39 +4688,39 @@
         <v>0.125</v>
       </c>
       <c r="C2">
-        <v>0.28666666666666668</v>
+        <v>0.2866666666666667</v>
       </c>
       <c r="D2">
-        <v>0.44333333333333341</v>
+        <v>0.4433333333333334</v>
       </c>
       <c r="E2">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="F2">
-        <v>0.61166666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.6116666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.26833333333333331</v>
+        <v>0.2683333333333333</v>
       </c>
       <c r="C3">
-        <v>0.54333333333333333</v>
+        <v>0.5433333333333333</v>
       </c>
       <c r="D3">
-        <v>0.68499999999999994</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="E3">
-        <v>0.73999999999999988</v>
+        <v>0.7399999999999999</v>
       </c>
       <c r="F3">
-        <v>0.77666666666666673</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7766666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -1531,124 +4728,124 @@
         <v>0.49</v>
       </c>
       <c r="C4">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D4">
-        <v>0.78833333333333344</v>
+        <v>0.7883333333333334</v>
       </c>
       <c r="E4">
-        <v>0.84333333333333327</v>
+        <v>0.8433333333333333</v>
       </c>
       <c r="F4">
-        <v>0.86499999999999988</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8649999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.59333333333333327</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="C5">
-        <v>0.76333333333333331</v>
+        <v>0.7633333333333333</v>
       </c>
       <c r="D5">
-        <v>0.85166666666666657</v>
+        <v>0.8516666666666666</v>
       </c>
       <c r="E5">
-        <v>0.87666666666666659</v>
+        <v>0.8766666666666666</v>
       </c>
       <c r="F5">
-        <v>0.88666666666666671</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8866666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.70500000000000007</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="C6">
-        <v>0.80000000000000016</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="D6">
         <v>0.8716666666666667</v>
       </c>
       <c r="E6">
-        <v>0.87333333333333341</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="F6">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.70833333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="C7">
-        <v>0.84666666666666668</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="D7">
-        <v>0.88166666666666671</v>
+        <v>0.8816666666666667</v>
       </c>
       <c r="E7">
-        <v>0.90499999999999992</v>
+        <v>0.9049999999999999</v>
       </c>
       <c r="F7">
         <v>0.92</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.76166666666666671</v>
+        <v>0.7616666666666667</v>
       </c>
       <c r="C8">
-        <v>0.84833333333333327</v>
+        <v>0.8483333333333333</v>
       </c>
       <c r="D8">
-        <v>0.90499999999999992</v>
+        <v>0.9049999999999999</v>
       </c>
       <c r="E8">
         <v>0.92</v>
       </c>
       <c r="F8">
-        <v>0.92833333333333334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.79333333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C9">
-        <v>0.89333333333333342</v>
+        <v>0.8933333333333334</v>
       </c>
       <c r="D9">
-        <v>0.91666666666666663</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E9">
-        <v>0.93166666666666664</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.93333333333333324</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9316666666666666</v>
+      </c>
+      <c r="F9">
+        <v>0.9333333333333332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.80833333333333346</v>
+        <v>0.8083333333333335</v>
       </c>
       <c r="C10">
         <v>0.8833333333333333</v>
@@ -1657,10 +4854,21 @@
         <v>0.91</v>
       </c>
       <c r="E10">
-        <v>0.92499999999999993</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="F10">
-        <v>0.92833333333333334</v>
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.9433333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -1669,11 +4877,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1693,7 +4901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1701,19 +4909,19 @@
         <v>0.12</v>
       </c>
       <c r="C2">
-        <v>0.33833333333333332</v>
+        <v>0.3383333333333333</v>
       </c>
       <c r="D2">
-        <v>0.52500000000000002</v>
+        <v>0.525</v>
       </c>
       <c r="E2">
-        <v>0.59166666666666667</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="F2">
-        <v>0.66333333333333333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.6633333333333333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
@@ -1721,50 +4929,50 @@
         <v>0.31</v>
       </c>
       <c r="C3">
-        <v>0.63666666666666671</v>
+        <v>0.6366666666666667</v>
       </c>
       <c r="D3">
-        <v>0.73166666666666658</v>
+        <v>0.7316666666666666</v>
       </c>
       <c r="E3">
-        <v>0.77166666666666661</v>
+        <v>0.7716666666666666</v>
       </c>
       <c r="F3">
-        <v>0.80833333333333324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8083333333333332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.55500000000000005</v>
+        <v>0.555</v>
       </c>
       <c r="C4">
-        <v>0.72666666666666657</v>
+        <v>0.7266666666666666</v>
       </c>
       <c r="D4">
-        <v>0.81500000000000006</v>
+        <v>0.8150000000000001</v>
       </c>
       <c r="E4">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F4">
-        <v>0.87333333333333341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8733333333333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.64333333333333331</v>
+        <v>0.6433333333333333</v>
       </c>
       <c r="C5">
         <v>0.77</v>
       </c>
       <c r="D5">
-        <v>0.85166666666666657</v>
+        <v>0.8516666666666666</v>
       </c>
       <c r="E5">
         <v>0.8783333333333333</v>
@@ -1773,27 +4981,27 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.71166666666666656</v>
+        <v>0.7116666666666666</v>
       </c>
       <c r="C6">
-        <v>0.83499999999999996</v>
+        <v>0.835</v>
       </c>
       <c r="D6">
-        <v>0.89666666666666661</v>
+        <v>0.8966666666666666</v>
       </c>
       <c r="E6">
-        <v>0.89666666666666661</v>
+        <v>0.8966666666666666</v>
       </c>
       <c r="F6">
-        <v>0.90833333333333333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9083333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
@@ -1801,59 +5009,59 @@
         <v>0.755</v>
       </c>
       <c r="C7">
-        <v>0.88166666666666671</v>
+        <v>0.8816666666666667</v>
       </c>
       <c r="D7">
         <v>0.8783333333333333</v>
       </c>
       <c r="E7">
-        <v>0.91999999999999993</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F7">
         <v>0.93</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="C8">
         <v>0.875</v>
       </c>
       <c r="D8">
-        <v>0.90333333333333332</v>
+        <v>0.9033333333333333</v>
       </c>
       <c r="E8">
-        <v>0.92500000000000016</v>
+        <v>0.9250000000000002</v>
       </c>
       <c r="F8">
-        <v>0.92666666666666675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9266666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="C9">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="D9">
         <v>0.9</v>
       </c>
       <c r="E9">
-        <v>0.92333333333333334</v>
+        <v>0.9233333333333333</v>
       </c>
       <c r="F9">
         <v>0.93</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
@@ -1861,16 +5069,30 @@
         <v>0.84</v>
       </c>
       <c r="C10">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="D10">
-        <v>0.92333333333333334</v>
+        <v>0.9233333333333333</v>
       </c>
       <c r="E10">
-        <v>0.93500000000000005</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F10" s="2">
-        <v>0.94000000000000006</v>
+        <v>0.9400000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="F11">
+        <v>0.9249999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1879,11 +5101,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1903,7 +5125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -1911,79 +5133,79 @@
         <v>0.1133333333333333</v>
       </c>
       <c r="C2">
-        <v>0.39333333333333331</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="D2">
         <v>0.6366666666666666</v>
       </c>
       <c r="E2">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F2">
-        <v>0.70166666666666666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7016666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.40500000000000003</v>
+        <v>0.405</v>
       </c>
       <c r="C3">
-        <v>0.67666666666666675</v>
+        <v>0.6766666666666667</v>
       </c>
       <c r="D3">
-        <v>0.76500000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="E3">
-        <v>0.80666666666666664</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F3">
-        <v>0.82333333333333325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8233333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.60499999999999998</v>
+        <v>0.605</v>
       </c>
       <c r="C4">
-        <v>0.73833333333333329</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="D4">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="E4">
-        <v>0.85666666666666658</v>
+        <v>0.8566666666666666</v>
       </c>
       <c r="F4">
-        <v>0.90333333333333332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9033333333333333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.67499999999999993</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="C5">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D5">
         <v>0.89</v>
       </c>
       <c r="E5">
-        <v>0.87666666666666659</v>
+        <v>0.8766666666666666</v>
       </c>
       <c r="F5">
-        <v>0.90666666666666673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9066666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
@@ -1991,59 +5213,59 @@
         <v>0.7416666666666667</v>
       </c>
       <c r="C6">
-        <v>0.85166666666666657</v>
+        <v>0.8516666666666666</v>
       </c>
       <c r="D6">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="E6">
         <v>0.9</v>
       </c>
       <c r="F6">
-        <v>0.92833333333333334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9283333333333333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.82833333333333325</v>
+        <v>0.8283333333333333</v>
       </c>
       <c r="C7">
-        <v>0.86833333333333329</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="D7">
         <v>0.91</v>
       </c>
       <c r="E7">
-        <v>0.92833333333333334</v>
+        <v>0.9283333333333333</v>
       </c>
       <c r="F7">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.81833333333333336</v>
+        <v>0.8183333333333334</v>
       </c>
       <c r="C8">
-        <v>0.89333333333333342</v>
+        <v>0.8933333333333334</v>
       </c>
       <c r="D8">
-        <v>0.90333333333333332</v>
+        <v>0.9033333333333333</v>
       </c>
       <c r="E8">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F8">
-        <v>0.92333333333333334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9233333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -2051,36 +5273,50 @@
         <v>0.84</v>
       </c>
       <c r="C9">
-        <v>0.89500000000000002</v>
+        <v>0.895</v>
       </c>
       <c r="D9">
-        <v>0.91666666666666663</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E9">
-        <v>0.92666666666666675</v>
+        <v>0.9266666666666667</v>
       </c>
       <c r="F9">
-        <v>0.93833333333333335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9383333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.85833333333333339</v>
+        <v>0.8583333333333334</v>
       </c>
       <c r="C10">
-        <v>0.92499999999999993</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="D10">
-        <v>0.94333333333333336</v>
+        <v>0.9433333333333334</v>
       </c>
       <c r="E10">
-        <v>0.93666666666666665</v>
+        <v>0.9366666666666666</v>
       </c>
       <c r="F10" s="2">
-        <v>0.95500000000000007</v>
+        <v>0.9550000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.9216666666666667</v>
+      </c>
+      <c r="E11">
+        <v>0.9416666666666665</v>
+      </c>
+      <c r="F11">
+        <v>0.955</v>
       </c>
     </row>
   </sheetData>
@@ -2089,11 +5325,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2113,7 +5349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -2121,139 +5357,139 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.37333333333333341</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="D2">
         <v>0.6166666666666667</v>
       </c>
       <c r="E2">
-        <v>0.64833333333333332</v>
+        <v>0.6483333333333333</v>
       </c>
       <c r="F2">
-        <v>0.69166666666666676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.6916666666666668</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.41833333333333328</v>
+        <v>0.4183333333333333</v>
       </c>
       <c r="C3">
-        <v>0.70666666666666667</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="D3">
-        <v>0.77666666666666673</v>
+        <v>0.7766666666666667</v>
       </c>
       <c r="E3">
-        <v>0.83000000000000007</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="F3">
-        <v>0.84333333333333338</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8433333333333334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.64666666666666661</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="C4">
-        <v>0.80833333333333324</v>
+        <v>0.8083333333333332</v>
       </c>
       <c r="D4">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="E4">
-        <v>0.86833333333333329</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="F4">
-        <v>0.89666666666666661</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8966666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.73666666666666669</v>
+        <v>0.7366666666666667</v>
       </c>
       <c r="C5">
-        <v>0.84166666666666667</v>
+        <v>0.8416666666666667</v>
       </c>
       <c r="D5">
-        <v>0.89500000000000002</v>
+        <v>0.895</v>
       </c>
       <c r="E5">
         <v>0.9</v>
       </c>
       <c r="F5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9166666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="C6">
-        <v>0.86333333333333329</v>
+        <v>0.8633333333333333</v>
       </c>
       <c r="D6">
-        <v>0.89166666666666661</v>
+        <v>0.8916666666666666</v>
       </c>
       <c r="E6">
         <v>0.91</v>
       </c>
       <c r="F6">
-        <v>0.91500000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.915</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.83000000000000007</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="C7">
         <v>0.89</v>
       </c>
       <c r="D7">
-        <v>0.91333333333333344</v>
+        <v>0.9133333333333334</v>
       </c>
       <c r="E7">
-        <v>0.92499999999999993</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="F7">
-        <v>0.92666666666666675</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9266666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.84500000000000008</v>
+        <v>0.8450000000000001</v>
       </c>
       <c r="C8">
-        <v>0.90499999999999992</v>
+        <v>0.9049999999999999</v>
       </c>
       <c r="D8">
-        <v>0.92166666666666675</v>
+        <v>0.9216666666666667</v>
       </c>
       <c r="E8">
-        <v>0.93166666666666664</v>
+        <v>0.9316666666666666</v>
       </c>
       <c r="F8">
-        <v>0.92500000000000016</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9250000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
@@ -2261,19 +5497,19 @@
         <v>0.86</v>
       </c>
       <c r="C9">
-        <v>0.91166666666666674</v>
+        <v>0.9116666666666667</v>
       </c>
       <c r="D9">
-        <v>0.92500000000000016</v>
+        <v>0.9250000000000002</v>
       </c>
       <c r="E9">
-        <v>0.94499999999999995</v>
+        <v>0.945</v>
       </c>
       <c r="F9">
-        <v>0.94833333333333325</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9483333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
@@ -2281,16 +5517,30 @@
         <v>0.89</v>
       </c>
       <c r="C10">
-        <v>0.92500000000000016</v>
+        <v>0.9250000000000002</v>
       </c>
       <c r="D10">
-        <v>0.93833333333333335</v>
+        <v>0.9383333333333334</v>
       </c>
       <c r="E10">
-        <v>0.94166666666666676</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.95000000000000007</v>
+        <v>0.9416666666666668</v>
+      </c>
+      <c r="F10">
+        <v>0.9500000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.9266666666666667</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.9633333333333333</v>
+      </c>
+      <c r="F11">
+        <v>0.9499999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2299,11 +5549,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2323,184 +5573,198 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.11166666666666671</v>
+        <v>0.1116666666666667</v>
       </c>
       <c r="C2">
-        <v>0.46166666666666673</v>
+        <v>0.4616666666666667</v>
       </c>
       <c r="D2">
         <v>0.68</v>
       </c>
       <c r="E2">
-        <v>0.69166666666666676</v>
+        <v>0.6916666666666668</v>
       </c>
       <c r="F2">
-        <v>0.73999999999999988</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.7399999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.38000000000000012</v>
+        <v>0.3800000000000001</v>
       </c>
       <c r="C3">
-        <v>0.69833333333333325</v>
+        <v>0.6983333333333333</v>
       </c>
       <c r="D3">
-        <v>0.80666666666666664</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="E3">
-        <v>0.84666666666666668</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="F3">
-        <v>0.86333333333333329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.8633333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0.67833333333333334</v>
+        <v>0.6783333333333333</v>
       </c>
       <c r="C4">
-        <v>0.81833333333333336</v>
+        <v>0.8183333333333334</v>
       </c>
       <c r="D4">
-        <v>0.86333333333333329</v>
+        <v>0.8633333333333333</v>
       </c>
       <c r="E4">
         <v>0.89</v>
       </c>
       <c r="F4">
-        <v>0.91500000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.915</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.75166666666666659</v>
+        <v>0.7516666666666666</v>
       </c>
       <c r="C5">
         <v>0.87</v>
       </c>
       <c r="D5">
-        <v>0.88166666666666671</v>
+        <v>0.8816666666666667</v>
       </c>
       <c r="E5">
         <v>0.91</v>
       </c>
       <c r="F5">
-        <v>0.91999999999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9199999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>0.77833333333333332</v>
+        <v>0.7783333333333333</v>
       </c>
       <c r="C6">
-        <v>0.89500000000000002</v>
+        <v>0.895</v>
       </c>
       <c r="D6">
-        <v>0.91833333333333333</v>
+        <v>0.9183333333333333</v>
       </c>
       <c r="E6">
-        <v>0.91333333333333344</v>
+        <v>0.9133333333333334</v>
       </c>
       <c r="F6">
-        <v>0.93500000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>0.81333333333333335</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C7">
-        <v>0.89500000000000002</v>
+        <v>0.895</v>
       </c>
       <c r="D7">
-        <v>0.91666666666666663</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E7">
-        <v>0.90833333333333333</v>
+        <v>0.9083333333333333</v>
       </c>
       <c r="F7">
-        <v>0.93666666666666665</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9366666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.85499999999999998</v>
+        <v>0.855</v>
       </c>
       <c r="C8">
-        <v>0.91833333333333333</v>
+        <v>0.9183333333333333</v>
       </c>
       <c r="D8">
-        <v>0.92333333333333334</v>
+        <v>0.9233333333333333</v>
       </c>
       <c r="E8">
-        <v>0.93666666666666665</v>
+        <v>0.9366666666666666</v>
       </c>
       <c r="F8">
-        <v>0.94833333333333325</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9483333333333333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>0.84833333333333327</v>
+        <v>0.8483333333333333</v>
       </c>
       <c r="C9">
-        <v>0.92833333333333334</v>
+        <v>0.9283333333333333</v>
       </c>
       <c r="D9">
         <v>0.93</v>
       </c>
       <c r="E9">
-        <v>0.95333333333333325</v>
+        <v>0.9533333333333333</v>
       </c>
       <c r="F9">
-        <v>0.93833333333333335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.9383333333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>36</v>
       </c>
       <c r="B10">
-        <v>0.87666666666666659</v>
+        <v>0.8766666666666666</v>
       </c>
       <c r="C10">
-        <v>0.92166666666666675</v>
+        <v>0.9216666666666667</v>
       </c>
       <c r="D10">
-        <v>0.93666666666666665</v>
+        <v>0.9366666666666666</v>
       </c>
       <c r="E10">
-        <v>0.95166666666666666</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.95666666666666667</v>
+        <v>0.9516666666666667</v>
+      </c>
+      <c r="F10">
+        <v>0.9566666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0.9283333333333333</v>
+      </c>
+      <c r="E11">
+        <v>0.9533333333333333</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.9633333333333333</v>
       </c>
     </row>
   </sheetData>
